--- a/public/documents/pieces-defense/Boissons-1-manquant-par-boisson.xlsx
+++ b/public/documents/pieces-defense/Boissons-1-manquant-par-boisson.xlsx
@@ -455,21 +455,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F68"/>
+  <dimension ref="A1:G69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Manquant par boisson : cout d'achat et CA pretendument perdu</t>
+          <t>Manquant = Achat - Conso - Stock fin (cout + CA pretendument perdu)</t>
         </is>
       </c>
     </row>
@@ -491,15 +492,20 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
+          <t>Stock fin L</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
           <t>Manquant L</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>Cout achat EUR</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>CA perdu EUR</t>
         </is>
@@ -518,12 +524,15 @@
         <v>470.8</v>
       </c>
       <c r="D3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="4" t="n">
         <v>335.4</v>
       </c>
-      <c r="E3" s="4" t="n">
+      <c r="F3" s="4" t="n">
         <v>6088</v>
       </c>
-      <c r="F3" s="4" t="n">
+      <c r="G3" s="4" t="n">
         <v>27395</v>
       </c>
     </row>
@@ -540,12 +549,15 @@
         <v>245.4</v>
       </c>
       <c r="D4" s="4" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="E4" s="4" t="n">
         <v>214.3</v>
       </c>
-      <c r="E4" s="4" t="n">
+      <c r="F4" s="4" t="n">
         <v>2728</v>
       </c>
-      <c r="F4" s="4" t="n">
+      <c r="G4" s="4" t="n">
         <v>11288</v>
       </c>
     </row>
@@ -562,12 +574,15 @@
         <v>286.8</v>
       </c>
       <c r="D5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="4" t="n">
         <v>394.2</v>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="F5" s="4" t="n">
         <v>2066</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="G5" s="4" t="n">
         <v>10250</v>
       </c>
     </row>
@@ -584,12 +599,15 @@
         <v>379.6</v>
       </c>
       <c r="D6" s="4" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="E6" s="4" t="n">
         <v>288.6</v>
       </c>
-      <c r="E6" s="4" t="n">
+      <c r="F6" s="4" t="n">
         <v>3175</v>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="G6" s="4" t="n">
         <v>9380</v>
       </c>
     </row>
@@ -606,12 +624,15 @@
         <v>1501</v>
       </c>
       <c r="D7" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="E7" s="4" t="n">
         <v>555</v>
       </c>
-      <c r="E7" s="4" t="n">
+      <c r="F7" s="4" t="n">
         <v>2192</v>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="G7" s="4" t="n">
         <v>8658</v>
       </c>
     </row>
@@ -622,19 +643,22 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>640</v>
+        <v>630</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>346.8</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>293.2</v>
+        <v>0</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>1554</v>
+        <v>283.2</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>7622</v>
+        <v>1501</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>7362</v>
       </c>
     </row>
     <row r="9">
@@ -650,12 +674,15 @@
         <v>161.9</v>
       </c>
       <c r="D9" s="4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E9" s="4" t="n">
         <v>55.3</v>
       </c>
-      <c r="E9" s="4" t="n">
+      <c r="F9" s="4" t="n">
         <v>1967</v>
       </c>
-      <c r="F9" s="4" t="n">
+      <c r="G9" s="4" t="n">
         <v>5534</v>
       </c>
     </row>
@@ -672,12 +699,15 @@
         <v>32.6</v>
       </c>
       <c r="D10" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="E10" s="4" t="n">
         <v>157.1</v>
       </c>
-      <c r="E10" s="4" t="n">
+      <c r="F10" s="4" t="n">
         <v>1629</v>
       </c>
-      <c r="F10" s="4" t="n">
+      <c r="G10" s="4" t="n">
         <v>5215</v>
       </c>
     </row>
@@ -694,12 +724,15 @@
         <v>346.1</v>
       </c>
       <c r="D11" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E11" s="4" t="n">
         <v>110.6</v>
       </c>
-      <c r="E11" s="4" t="n">
+      <c r="F11" s="4" t="n">
         <v>1498</v>
       </c>
-      <c r="F11" s="4" t="n">
+      <c r="G11" s="4" t="n">
         <v>4721</v>
       </c>
     </row>
@@ -716,12 +749,15 @@
         <v>97.90000000000001</v>
       </c>
       <c r="D12" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="E12" s="4" t="n">
         <v>192.3</v>
       </c>
-      <c r="E12" s="4" t="n">
+      <c r="F12" s="4" t="n">
         <v>1650</v>
       </c>
-      <c r="F12" s="4" t="n">
+      <c r="G12" s="4" t="n">
         <v>4616</v>
       </c>
     </row>
@@ -738,12 +774,15 @@
         <v>7</v>
       </c>
       <c r="D13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="E13" s="4" t="n">
+      <c r="F13" s="4" t="n">
         <v>440</v>
       </c>
-      <c r="F13" s="4" t="n">
+      <c r="G13" s="4" t="n">
         <v>4562</v>
       </c>
     </row>
@@ -760,12 +799,15 @@
         <v>190.8</v>
       </c>
       <c r="D14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="4" t="n">
         <v>169.2</v>
       </c>
-      <c r="E14" s="4" t="n">
+      <c r="F14" s="4" t="n">
         <v>518</v>
       </c>
-      <c r="F14" s="4" t="n">
+      <c r="G14" s="4" t="n">
         <v>4400</v>
       </c>
     </row>
@@ -782,12 +824,15 @@
         <v>429.5</v>
       </c>
       <c r="D15" s="4" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="E15" s="4" t="n">
         <v>76.8</v>
       </c>
-      <c r="E15" s="4" t="n">
+      <c r="F15" s="4" t="n">
         <v>1302</v>
       </c>
-      <c r="F15" s="4" t="n">
+      <c r="G15" s="4" t="n">
         <v>3685</v>
       </c>
     </row>
@@ -804,12 +849,15 @@
         <v>103.8</v>
       </c>
       <c r="D16" s="4" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E16" s="4" t="n">
         <v>90.59999999999999</v>
       </c>
-      <c r="E16" s="4" t="n">
+      <c r="F16" s="4" t="n">
         <v>1386</v>
       </c>
-      <c r="F16" s="4" t="n">
+      <c r="G16" s="4" t="n">
         <v>3502</v>
       </c>
     </row>
@@ -826,12 +874,15 @@
         <v>165.2</v>
       </c>
       <c r="D17" s="4" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="E17" s="4" t="n">
         <v>66.59999999999999</v>
       </c>
-      <c r="E17" s="4" t="n">
+      <c r="F17" s="4" t="n">
         <v>1196</v>
       </c>
-      <c r="F17" s="4" t="n">
+      <c r="G17" s="4" t="n">
         <v>3197</v>
       </c>
     </row>
@@ -848,12 +899,15 @@
         <v>78.5</v>
       </c>
       <c r="D18" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E18" s="4" t="n">
         <v>34.8</v>
       </c>
-      <c r="E18" s="4" t="n">
+      <c r="F18" s="4" t="n">
         <v>377</v>
       </c>
-      <c r="F18" s="4" t="n">
+      <c r="G18" s="4" t="n">
         <v>2203</v>
       </c>
     </row>
@@ -870,12 +924,15 @@
         <v>92.5</v>
       </c>
       <c r="D19" s="4" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="E19" s="4" t="n">
         <v>140.6</v>
       </c>
-      <c r="E19" s="4" t="n">
+      <c r="F19" s="4" t="n">
         <v>607</v>
       </c>
-      <c r="F19" s="4" t="n">
+      <c r="G19" s="4" t="n">
         <v>2045</v>
       </c>
     </row>
@@ -892,12 +949,15 @@
         <v>139.8</v>
       </c>
       <c r="D20" s="4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E20" s="4" t="n">
         <v>47</v>
       </c>
-      <c r="E20" s="4" t="n">
+      <c r="F20" s="4" t="n">
         <v>529</v>
       </c>
-      <c r="F20" s="4" t="n">
+      <c r="G20" s="4" t="n">
         <v>1973</v>
       </c>
     </row>
@@ -914,12 +974,15 @@
         <v>5.4</v>
       </c>
       <c r="D21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="4" t="n">
         <v>11.4</v>
       </c>
-      <c r="E21" s="4" t="n">
+      <c r="F21" s="4" t="n">
         <v>277</v>
       </c>
-      <c r="F21" s="4" t="n">
+      <c r="G21" s="4" t="n">
         <v>1849</v>
       </c>
     </row>
@@ -936,12 +999,15 @@
         <v>3.2</v>
       </c>
       <c r="D22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="E22" s="4" t="n">
+      <c r="F22" s="4" t="n">
         <v>298</v>
       </c>
-      <c r="F22" s="4" t="n">
+      <c r="G22" s="4" t="n">
         <v>1815</v>
       </c>
     </row>
@@ -958,167 +1024,191 @@
         <v>172.1</v>
       </c>
       <c r="D23" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E23" s="4" t="n">
         <v>24.4</v>
       </c>
-      <c r="E23" s="4" t="n">
+      <c r="F23" s="4" t="n">
         <v>405</v>
       </c>
-      <c r="F23" s="4" t="n">
+      <c r="G23" s="4" t="n">
         <v>1285</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Cidre Brut</t>
+          <t>Génépi</t>
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>207</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>125.2</v>
+        <v>2.3</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>65.2</v>
+        <v>0.7</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>333</v>
+        <v>6.8</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1218</v>
+        <v>219</v>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>1102</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Génépi</t>
+          <t>Get 27</t>
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>6.8</v>
+        <v>0.7</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>219</v>
+        <v>8</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1102</v>
+        <v>127</v>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>1037</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>Get 27</t>
+          <t>Rouget de Lisle Blanche 33cl</t>
         </is>
       </c>
       <c r="B26" s="4" t="n">
-        <v>12</v>
+        <v>195.3</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>3.3</v>
+        <v>136.5</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>127</v>
+        <v>55.9</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>1037</v>
+        <v>297</v>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>999</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>Rouget de Lisle Blanche 33cl</t>
+          <t>Vin de Paille</t>
         </is>
       </c>
       <c r="B27" s="4" t="n">
-        <v>195.3</v>
+        <v>36.4</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>136.5</v>
+        <v>24.9</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>55.9</v>
+        <v>3</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>297</v>
+        <v>8.5</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>999</v>
+        <v>411</v>
+      </c>
+      <c r="G27" s="4" t="n">
+        <v>853</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>Vin de Paille</t>
+          <t>Hautes Côtes de Nuits blanc</t>
         </is>
       </c>
       <c r="B28" s="4" t="n">
-        <v>36.4</v>
+        <v>18</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>24.9</v>
+        <v>2.2</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>411</v>
+        <v>15.8</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>853</v>
+        <v>257</v>
+      </c>
+      <c r="G28" s="4" t="n">
+        <v>830</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>Hautes Côtes de Nuits blanc</t>
+          <t>Rouget de Lisle Ambrée 33cl</t>
         </is>
       </c>
       <c r="B29" s="4" t="n">
-        <v>18</v>
+        <v>182.2</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>2.2</v>
+        <v>127.7</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>15.8</v>
+        <v>8.9</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>257</v>
+        <v>45.6</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>830</v>
+        <v>248</v>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v>815</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>Rouget de Lisle Ambrée 33cl</t>
+          <t>Cidre Brut</t>
         </is>
       </c>
       <c r="B30" s="4" t="n">
-        <v>182.2</v>
+        <v>184.5</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>127.7</v>
+        <v>125.2</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>45.6</v>
+        <v>16.5</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>248</v>
+        <v>42.8</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>815</v>
+        <v>218</v>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>798</v>
       </c>
     </row>
     <row r="31">
@@ -1134,12 +1224,15 @@
         <v>16.6</v>
       </c>
       <c r="D31" s="4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E31" s="4" t="n">
         <v>5.1</v>
       </c>
-      <c r="E31" s="4" t="n">
+      <c r="F31" s="4" t="n">
         <v>99</v>
       </c>
-      <c r="F31" s="4" t="n">
+      <c r="G31" s="4" t="n">
         <v>664</v>
       </c>
     </row>
@@ -1156,12 +1249,15 @@
         <v>1.1</v>
       </c>
       <c r="D32" s="4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E32" s="4" t="n">
         <v>3.8</v>
       </c>
-      <c r="E32" s="4" t="n">
+      <c r="F32" s="4" t="n">
         <v>109</v>
       </c>
-      <c r="F32" s="4" t="n">
+      <c r="G32" s="4" t="n">
         <v>614</v>
       </c>
     </row>
@@ -1178,12 +1274,15 @@
         <v>5.2</v>
       </c>
       <c r="D33" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" s="4" t="n">
         <v>2.8</v>
       </c>
-      <c r="E33" s="4" t="n">
+      <c r="F33" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="F33" s="4" t="n">
+      <c r="G33" s="4" t="n">
         <v>532</v>
       </c>
     </row>
@@ -1200,12 +1299,15 @@
         <v>26.2</v>
       </c>
       <c r="D34" s="4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="E34" s="4" t="n">
         <v>12.7</v>
       </c>
-      <c r="E34" s="4" t="n">
+      <c r="F34" s="4" t="n">
         <v>109</v>
       </c>
-      <c r="F34" s="4" t="n">
+      <c r="G34" s="4" t="n">
         <v>489</v>
       </c>
     </row>
@@ -1222,12 +1324,15 @@
         <v>5.9</v>
       </c>
       <c r="D35" s="4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E35" s="4" t="n">
         <v>3.2</v>
       </c>
-      <c r="E35" s="4" t="n">
+      <c r="F35" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="F35" s="4" t="n">
+      <c r="G35" s="4" t="n">
         <v>470</v>
       </c>
     </row>
@@ -1244,12 +1349,15 @@
         <v>5.8</v>
       </c>
       <c r="D36" s="4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E36" s="4" t="n">
         <v>3.3</v>
       </c>
-      <c r="E36" s="4" t="n">
+      <c r="F36" s="4" t="n">
         <v>97</v>
       </c>
-      <c r="F36" s="4" t="n">
+      <c r="G36" s="4" t="n">
         <v>432</v>
       </c>
     </row>
@@ -1266,12 +1374,15 @@
         <v>107.6</v>
       </c>
       <c r="D37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="4" t="n">
         <v>18.4</v>
       </c>
-      <c r="E37" s="4" t="n">
+      <c r="F37" s="4" t="n">
         <v>66</v>
       </c>
-      <c r="F37" s="4" t="n">
+      <c r="G37" s="4" t="n">
         <v>392</v>
       </c>
     </row>
@@ -1288,12 +1399,15 @@
         <v>3</v>
       </c>
       <c r="D38" s="4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E38" s="4" t="n">
         <v>1.9</v>
       </c>
-      <c r="E38" s="4" t="n">
+      <c r="F38" s="4" t="n">
         <v>53</v>
       </c>
-      <c r="F38" s="4" t="n">
+      <c r="G38" s="4" t="n">
         <v>360</v>
       </c>
     </row>
@@ -1310,12 +1424,15 @@
         <v>0.9</v>
       </c>
       <c r="D39" s="4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E39" s="4" t="n">
         <v>2.6</v>
       </c>
-      <c r="E39" s="4" t="n">
+      <c r="F39" s="4" t="n">
         <v>75</v>
       </c>
-      <c r="F39" s="4" t="n">
+      <c r="G39" s="4" t="n">
         <v>335</v>
       </c>
     </row>
@@ -1332,12 +1449,15 @@
         <v>9.800000000000001</v>
       </c>
       <c r="D40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="4" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="E40" s="4" t="n">
+      <c r="F40" s="4" t="n">
         <v>58</v>
       </c>
-      <c r="F40" s="4" t="n">
+      <c r="G40" s="4" t="n">
         <v>242</v>
       </c>
     </row>
@@ -1354,386 +1474,440 @@
         <v>15</v>
       </c>
       <c r="D41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="4" t="n">
         <v>3.7</v>
       </c>
-      <c r="E41" s="4" t="n">
+      <c r="F41" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="F41" s="4" t="n">
+      <c r="G41" s="4" t="n">
         <v>143</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>Grand Marnier</t>
+          <t>Pastis 51</t>
         </is>
       </c>
       <c r="B42" s="4" t="n">
-        <v>10.5</v>
+        <v>6</v>
       </c>
       <c r="C42" s="4" t="n">
-        <v>8.1</v>
+        <v>4.3</v>
       </c>
       <c r="D42" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>31</v>
+        <v>0.7</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>130</v>
+        <v>11</v>
+      </c>
+      <c r="G42" s="4" t="n">
+        <v>129</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>Pastis 51</t>
+          <t>Bordeaux Supérieur</t>
         </is>
       </c>
       <c r="B43" s="4" t="n">
-        <v>6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="C43" s="4" t="n">
-        <v>4.3</v>
+        <v>6.8</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>11</v>
+        <v>1.4</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>129</v>
+        <v>12</v>
+      </c>
+      <c r="G43" s="4" t="n">
+        <v>70</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>Bordeaux Supérieur</t>
+          <t>Cubis de vin (couleur non précisée)</t>
         </is>
       </c>
       <c r="B44" s="4" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="C44" s="4" t="n">
-        <v>6.8</v>
+        <v>426.9</v>
       </c>
       <c r="D44" s="4" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>12</v>
+        <v>-426.9</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>70</v>
+        <v>0</v>
+      </c>
+      <c r="G44" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>Cubis de vin (couleur non précisée)</t>
+          <t>Arbois Béthanie</t>
         </is>
       </c>
       <c r="B45" s="4" t="n">
-        <v>0</v>
+        <v>214.5</v>
       </c>
       <c r="C45" s="4" t="n">
-        <v>426.9</v>
+        <v>309.9</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>-426.9</v>
+        <v>0</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>0</v>
+        <v>-95.40000000000001</v>
       </c>
       <c r="F45" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>Arbois Béthanie</t>
+          <t>Ravelin</t>
         </is>
       </c>
       <c r="B46" s="4" t="n">
-        <v>214.5</v>
+        <v>319.5</v>
       </c>
       <c r="C46" s="4" t="n">
-        <v>309.9</v>
+        <v>251.8</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>-95.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>0</v>
+        <v>67.7</v>
       </c>
       <c r="F46" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="G46" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>Ravelin</t>
+          <t>Calvados</t>
         </is>
       </c>
       <c r="B47" s="4" t="n">
-        <v>319.5</v>
+        <v>73</v>
       </c>
       <c r="C47" s="4" t="n">
-        <v>251.8</v>
+        <v>120.5</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>67.7</v>
+        <v>1</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>200</v>
+        <v>-48.5</v>
       </c>
       <c r="F47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>Calvados</t>
+          <t>Gewurztraminer</t>
         </is>
       </c>
       <c r="B48" s="4" t="n">
-        <v>73</v>
+        <v>6</v>
       </c>
       <c r="C48" s="4" t="n">
-        <v>120.5</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>-48.5</v>
+        <v>2.2</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>0</v>
+        <v>-75.09999999999999</v>
       </c>
       <c r="F48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>Gewurztraminer</t>
+          <t>Chablis</t>
         </is>
       </c>
       <c r="B49" s="4" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="C49" s="4" t="n">
-        <v>78.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="D49" s="4" t="n">
-        <v>-75.09999999999999</v>
+        <v>12</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>0</v>
+        <v>-67.7</v>
       </c>
       <c r="F49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>Chablis</t>
+          <t>Crème de Cassis</t>
         </is>
       </c>
       <c r="B50" s="4" t="n">
-        <v>18</v>
+        <v>132.7</v>
       </c>
       <c r="C50" s="4" t="n">
-        <v>73.7</v>
+        <v>69</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>-67.7</v>
+        <v>0</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>0</v>
+        <v>63.7</v>
       </c>
       <c r="F50" s="4" t="n">
+        <v>585</v>
+      </c>
+      <c r="G50" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>Crème de Cassis</t>
+          <t>Picon</t>
         </is>
       </c>
       <c r="B51" s="4" t="n">
-        <v>132.7</v>
+        <v>72</v>
       </c>
       <c r="C51" s="4" t="n">
-        <v>69</v>
+        <v>28.3</v>
       </c>
       <c r="D51" s="4" t="n">
-        <v>63.7</v>
+        <v>0</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>585</v>
+        <v>43.7</v>
       </c>
       <c r="F51" s="4" t="n">
+        <v>454</v>
+      </c>
+      <c r="G51" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>Picon</t>
+          <t>Soho Litchi</t>
         </is>
       </c>
       <c r="B52" s="4" t="n">
-        <v>72</v>
+        <v>52.5</v>
       </c>
       <c r="C52" s="4" t="n">
-        <v>28.3</v>
+        <v>23.3</v>
       </c>
       <c r="D52" s="4" t="n">
-        <v>43.7</v>
+        <v>0.7</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>454</v>
+        <v>28.5</v>
       </c>
       <c r="F52" s="4" t="n">
+        <v>411</v>
+      </c>
+      <c r="G52" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>Soho Litchi</t>
+          <t>Liqueur de Cerise</t>
         </is>
       </c>
       <c r="B53" s="4" t="n">
-        <v>52.5</v>
+        <v>12.7</v>
       </c>
       <c r="C53" s="4" t="n">
-        <v>23.3</v>
+        <v>16.1</v>
       </c>
       <c r="D53" s="4" t="n">
-        <v>28.5</v>
+        <v>1.4</v>
       </c>
       <c r="E53" s="4" t="n">
-        <v>411</v>
+        <v>-4.8</v>
       </c>
       <c r="F53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>Liqueur de Cerise</t>
+          <t>Martini Blanc</t>
         </is>
       </c>
       <c r="B54" s="4" t="n">
-        <v>12.7</v>
+        <v>13</v>
       </c>
       <c r="C54" s="4" t="n">
-        <v>16.1</v>
+        <v>12.6</v>
       </c>
       <c r="D54" s="4" t="n">
-        <v>-4.8</v>
+        <v>1</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>0</v>
+        <v>-0.6</v>
       </c>
       <c r="F54" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>Martini Blanc</t>
+          <t>Côtes de Provence Rosé Minuty</t>
         </is>
       </c>
       <c r="B55" s="4" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C55" s="4" t="n">
-        <v>12.6</v>
+        <v>11.2</v>
       </c>
       <c r="D55" s="4" t="n">
-        <v>-0.6</v>
+        <v>3.8</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F55" s="4" t="n">
+        <v>104</v>
+      </c>
+      <c r="G55" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>Côtes de Provence Rosé Minuty</t>
+          <t>Vodka</t>
         </is>
       </c>
       <c r="B56" s="4" t="n">
-        <v>21</v>
+        <v>32.9</v>
       </c>
       <c r="C56" s="4" t="n">
-        <v>11.2</v>
+        <v>10.7</v>
       </c>
       <c r="D56" s="4" t="n">
-        <v>6</v>
+        <v>0.7</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>104</v>
+        <v>21.6</v>
       </c>
       <c r="F56" s="4" t="n">
+        <v>295</v>
+      </c>
+      <c r="G56" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>Vodka</t>
+          <t>Passoa</t>
         </is>
       </c>
       <c r="B57" s="4" t="n">
-        <v>32.9</v>
+        <v>15.4</v>
       </c>
       <c r="C57" s="4" t="n">
-        <v>10.7</v>
+        <v>10.1</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>21.6</v>
+        <v>1.4</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>295</v>
+        <v>3.9</v>
       </c>
       <c r="F57" s="4" t="n">
+        <v>53</v>
+      </c>
+      <c r="G57" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>Passoa</t>
+          <t>Grand Marnier</t>
         </is>
       </c>
       <c r="B58" s="4" t="n">
-        <v>15.4</v>
+        <v>8.4</v>
       </c>
       <c r="C58" s="4" t="n">
-        <v>10.1</v>
+        <v>8.1</v>
       </c>
       <c r="D58" s="4" t="n">
-        <v>3.9</v>
+        <v>1.4</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>53</v>
+        <v>-1.1</v>
       </c>
       <c r="F58" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1750,12 +1924,15 @@
         <v>6</v>
       </c>
       <c r="D59" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" s="4" t="n">
         <v>-6</v>
       </c>
-      <c r="E59" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="F59" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1772,12 +1949,15 @@
         <v>5.2</v>
       </c>
       <c r="D60" s="4" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="E60" s="4" t="n">
         <v>14.3</v>
       </c>
-      <c r="E60" s="4" t="n">
+      <c r="F60" s="4" t="n">
         <v>724</v>
       </c>
-      <c r="F60" s="4" t="n">
+      <c r="G60" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1794,12 +1974,15 @@
         <v>4.5</v>
       </c>
       <c r="D61" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" s="4" t="n">
         <v>-4.5</v>
       </c>
-      <c r="E61" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="F61" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1816,12 +1999,15 @@
         <v>2.4</v>
       </c>
       <c r="D62" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" s="4" t="n">
         <v>-2.4</v>
       </c>
-      <c r="E62" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="F62" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1838,12 +2024,15 @@
         <v>1.7</v>
       </c>
       <c r="D63" s="4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E63" s="4" t="n">
         <v>-2.4</v>
       </c>
-      <c r="E63" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="F63" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1860,12 +2049,15 @@
         <v>1.3</v>
       </c>
       <c r="D64" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" s="4" t="n">
         <v>2.2</v>
       </c>
-      <c r="E64" s="4" t="n">
+      <c r="F64" s="4" t="n">
         <v>48</v>
       </c>
-      <c r="F64" s="4" t="n">
+      <c r="G64" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1882,12 +2074,15 @@
         <v>0.9</v>
       </c>
       <c r="D65" s="4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E65" s="4" t="n">
         <v>-1.6</v>
       </c>
-      <c r="E65" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="F65" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1904,12 +2099,15 @@
         <v>0.8</v>
       </c>
       <c r="D66" s="4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E66" s="4" t="n">
         <v>-1.5</v>
       </c>
-      <c r="E66" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="F66" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1926,36 +2124,55 @@
         <v>0</v>
       </c>
       <c r="D67" s="4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E67" s="4" t="n">
         <v>-1.4</v>
       </c>
-      <c r="E67" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="F67" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>TOTAL (manquant positif)</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr"/>
       <c r="C68" s="5" t="inlineStr"/>
-      <c r="D68" s="6" t="n">
-        <v>3822</v>
-      </c>
+      <c r="D68" s="5" t="inlineStr"/>
       <c r="E68" s="6" t="n">
-        <v>37518</v>
+        <v>3788</v>
       </c>
       <c r="F68" s="6" t="n">
-        <v>137051</v>
-      </c>
+        <v>37319</v>
+      </c>
+      <c r="G68" s="6" t="n">
+        <v>136241</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL NET (lignes negatives incluses)</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="inlineStr"/>
+      <c r="C69" s="5" t="inlineStr"/>
+      <c r="D69" s="5" t="inlineStr"/>
+      <c r="E69" s="6" t="n">
+        <v>3048</v>
+      </c>
+      <c r="F69" s="5" t="inlineStr"/>
+      <c r="G69" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
